--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\for_github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338E026F-B78A-46C9-B3C5-86F3D27D90A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A237EB-EE57-48B3-BA25-136944A1325C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t>Neutral</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -398,12 +401,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -887,74 +890,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12600682</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1065,7 +1068,7 @@
       <c r="F7" s="14">
         <v>180</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="18">
         <v>5</v>
       </c>
       <c r="H7" s="14">
@@ -1083,7 +1086,7 @@
         <v>57</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M7" s="16" t="s">
         <v>51</v>
@@ -1093,26 +1096,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>50</v>
+      </c>
+      <c r="E8" s="14">
+        <v>20</v>
+      </c>
+      <c r="F8" s="14">
+        <v>160</v>
+      </c>
+      <c r="G8" s="14">
+        <v>50</v>
+      </c>
+      <c r="H8" s="14">
+        <v>20</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>740</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="13"/>

--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\for_github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A237EB-EE57-48B3-BA25-136944A1325C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0D526F-4C5F-40F5-A5E4-CA493B4DE2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Felt a bit tired after evening class</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1118,7 @@
         <v>160</v>
       </c>
       <c r="G8" s="14">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="H8" s="14">
         <v>20</v>
@@ -1141,27 +1144,51 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+    <row r="9" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B9" s="14">
+        <v>430</v>
+      </c>
+      <c r="C9" s="14">
+        <v>60</v>
+      </c>
+      <c r="D9" s="14">
+        <v>40</v>
+      </c>
+      <c r="E9" s="14">
+        <v>40</v>
+      </c>
+      <c r="F9" s="14">
+        <v>200</v>
+      </c>
+      <c r="G9" s="14">
+        <v>6</v>
+      </c>
+      <c r="H9" s="14">
+        <v>30</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13"/>

--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0D526F-4C5F-40F5-A5E4-CA493B4DE2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579D5D26-0C11-4DDC-88AE-C3FE8A80E0BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -217,6 +217,12 @@
   </si>
   <si>
     <t>Felt a bit tired after evening class</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>feels good</t>
   </si>
 </sst>
 </file>
@@ -1191,26 +1197,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B10" s="14">
+        <v>450</v>
+      </c>
+      <c r="C10" s="14">
+        <v>50</v>
+      </c>
+      <c r="D10" s="14">
+        <v>30</v>
+      </c>
+      <c r="E10" s="14">
+        <v>50</v>
+      </c>
+      <c r="F10" s="14">
+        <v>160</v>
+      </c>
+      <c r="G10" s="14">
+        <v>7</v>
+      </c>
+      <c r="H10" s="14">
+        <v>40</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13"/>
@@ -1232,7 +1262,6 @@
       <c r="K11" s="16"/>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13"/>

--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579D5D26-0C11-4DDC-88AE-C3FE8A80E0BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6F900D-596B-4089-8A68-6D28ECCA9B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,12 @@
   <si>
     <t>feels good</t>
   </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>feels tired for doing too much coding</t>
+  </si>
 </sst>
 </file>
 
@@ -342,7 +348,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -365,11 +371,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -416,6 +433,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1242,26 +1262,51 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+    <row r="11" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B11" s="14">
+        <v>460</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>20</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14">
+        <v>180</v>
+      </c>
+      <c r="G11" s="14">
+        <v>4</v>
+      </c>
+      <c r="H11" s="14">
+        <v>50</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>640</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11" s="22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13"/>

--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6F900D-596B-4089-8A68-6D28ECCA9B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085148F3-A42E-451D-A778-DD36D036E009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,6 +229,12 @@
   </si>
   <si>
     <t>feels tired for doing too much coding</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>happy</t>
   </si>
 </sst>
 </file>
@@ -430,12 +436,12 @@
     <xf numFmtId="1" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -919,74 +925,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="22">
         <v>12600682</v>
       </c>
-      <c r="G2" s="21"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
     </row>
     <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1304,31 +1310,55 @@
       <c r="M11" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N11" s="22" t="s">
+      <c r="N11" s="19" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B12" s="14">
+        <v>420</v>
+      </c>
+      <c r="C12" s="14">
+        <v>50</v>
+      </c>
+      <c r="D12" s="14">
+        <v>50</v>
+      </c>
+      <c r="E12" s="14">
+        <v>20</v>
+      </c>
+      <c r="F12" s="14">
+        <v>250</v>
+      </c>
+      <c r="G12" s="14">
+        <v>5</v>
+      </c>
+      <c r="H12" s="14">
+        <v>30</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13"/>

--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085148F3-A42E-451D-A778-DD36D036E009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B93EA3F-7918-4F34-A617-8591EC9B348A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>happy</t>
+  </si>
+  <si>
+    <t>tired</t>
   </si>
 </sst>
 </file>
@@ -1361,26 +1364,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B13" s="14">
+        <v>480</v>
+      </c>
+      <c r="C13" s="14">
+        <v>50</v>
+      </c>
+      <c r="D13" s="14">
+        <v>80</v>
+      </c>
+      <c r="E13" s="14">
+        <v>30</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="14">
+        <v>20</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>

--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B93EA3F-7918-4F34-A617-8591EC9B348A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669EB907-17BE-4097-8487-E57972A06935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>tired</t>
+  </si>
+  <si>
+    <t>not feeling good for some health issues</t>
   </si>
 </sst>
 </file>
@@ -1409,27 +1412,51 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B14" s="14">
+        <v>500</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>40</v>
+      </c>
+      <c r="E14" s="14">
+        <v>35</v>
+      </c>
+      <c r="F14" s="14">
+        <v>250</v>
+      </c>
+      <c r="G14" s="14">
+        <v>5</v>
+      </c>
+      <c r="H14" s="14">
+        <v>50</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>905</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>535</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>

--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669EB907-17BE-4097-8487-E57972A06935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28632647-F6F7-4AF3-BA57-4A508B10668B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>not feeling good for some health issues</t>
+  </si>
+  <si>
+    <t>Learned basics of c++ language.</t>
   </si>
 </sst>
 </file>
@@ -1459,26 +1462,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B15" s="14">
+        <v>450</v>
+      </c>
+      <c r="C15" s="14">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>40</v>
+      </c>
+      <c r="E15" s="14">
+        <v>90</v>
+      </c>
+      <c r="F15" s="14">
+        <v>350</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>10</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>

--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28632647-F6F7-4AF3-BA57-4A508B10668B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE58012B-17CB-44C1-887A-7765BEA60B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,12 @@
   </si>
   <si>
     <t>Learned basics of c++ language.</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Felt tired attending 6 classes in one strecth</t>
   </si>
 </sst>
 </file>
@@ -1507,27 +1513,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+    <row r="16" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>60</v>
+      </c>
+      <c r="E16" s="14">
+        <v>20</v>
+      </c>
+      <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="14">
+        <v>50</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>

--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE58012B-17CB-44C1-887A-7765BEA60B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA918C7-5C11-4EBC-80BA-ED626AA23D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>Felt tired attending 6 classes in one strecth</t>
+  </si>
+  <si>
+    <t>good</t>
   </si>
 </sst>
 </file>
@@ -1560,26 +1563,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B17" s="14">
+        <v>400</v>
+      </c>
+      <c r="C17" s="14">
+        <v>10</v>
+      </c>
+      <c r="D17" s="14">
+        <v>65</v>
+      </c>
+      <c r="E17" s="14">
+        <v>50</v>
+      </c>
+      <c r="F17" s="14">
+        <v>250</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>60</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>835</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>605</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>

--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA918C7-5C11-4EBC-80BA-ED626AA23D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E44DA418-6958-4C0E-8604-A13AAEE46417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,12 @@
   </si>
   <si>
     <t>good</t>
+  </si>
+  <si>
+    <t>j20</t>
+  </si>
+  <si>
+    <t>Too much tired due to less sleep</t>
   </si>
 </sst>
 </file>
@@ -1609,26 +1615,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B18" s="14">
+        <v>380</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>20</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>400</v>
+      </c>
+      <c r="G18" s="14">
+        <v>8</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13"/>

--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E44DA418-6958-4C0E-8604-A13AAEE46417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD185F6-66E6-4F25-9761-361BE117DAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -255,10 +255,13 @@
     <t>good</t>
   </si>
   <si>
-    <t>j20</t>
+    <t>Too much tired due to less sleep</t>
   </si>
   <si>
-    <t>Too much tired due to less sleep</t>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Feels good</t>
   </si>
 </sst>
 </file>
@@ -1636,16 +1639,16 @@
       <c r="G18" s="14">
         <v>8</v>
       </c>
-      <c r="H18" s="14" t="s">
-        <v>72</v>
+      <c r="H18" s="14">
+        <v>20</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>860</v>
+        <v>880</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>58</v>
@@ -1657,30 +1660,54 @@
         <v>51</v>
       </c>
       <c r="N18" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B19" s="14">
+        <v>400</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>30</v>
+      </c>
+      <c r="E19" s="14">
+        <v>70</v>
+      </c>
+      <c r="F19" s="14">
+        <v>200</v>
+      </c>
+      <c r="G19" s="14">
+        <v>4</v>
+      </c>
+      <c r="H19" s="14">
+        <v>50</v>
+      </c>
+      <c r="I19" s="15">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J19" s="15">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+      <c r="M19" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>

--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD185F6-66E6-4F25-9761-361BE117DAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DE293D-DD14-4C43-AA22-0847CDF84B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1710,26 +1710,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>50</v>
+      </c>
+      <c r="E20" s="14">
+        <v>40</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14">
+        <v>25</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>815</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>625</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>

--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DE293D-DD14-4C43-AA22-0847CDF84B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8CE6FB-25A0-44DC-BB2C-6FE029037288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,12 @@
   </si>
   <si>
     <t>Feels good</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>😊</t>
   </si>
 </sst>
 </file>
@@ -1756,26 +1762,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B21" s="14">
+        <v>450</v>
+      </c>
+      <c r="C21" s="14">
+        <v>20</v>
+      </c>
+      <c r="D21" s="14">
+        <v>40</v>
+      </c>
+      <c r="E21" s="14">
+        <v>65</v>
+      </c>
+      <c r="F21" s="14">
+        <v>300</v>
+      </c>
+      <c r="G21" s="14">
+        <v>6</v>
+      </c>
+      <c r="H21" s="14">
+        <v>40</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>915</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>525</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13"/>

--- a/my_data1.xlsx
+++ b/my_data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manaal\Desktop\CAP\CAP776\project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8CE6FB-25A0-44DC-BB2C-6FE029037288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD676A2-A754-483E-86BA-FCD191093151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>😊</t>
+  </si>
+  <si>
+    <t>productive</t>
   </si>
 </sst>
 </file>
@@ -1808,26 +1811,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B22" s="14">
+        <v>400</v>
+      </c>
+      <c r="C22" s="14">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>30</v>
+      </c>
+      <c r="E22" s="14">
+        <v>50</v>
+      </c>
+      <c r="F22" s="14">
+        <v>250</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>50</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>
